--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_antofagasta_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_antofagasta_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-04 13:55</t>
+    <t xml:space="preserve">2026-08-07 06:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_antofagasta_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_antofagasta_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-07 06:21</t>
+    <t xml:space="preserve">2026-08-13 12:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_antofagasta_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_antofagasta_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-13 12:40</t>
+    <t xml:space="preserve">2026-08-19 11:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_antofagasta_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_antofagasta_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 11:41</t>
+    <t xml:space="preserve">2026-08-28 10:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_antofagasta_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_antofagasta_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 10:50</t>
+    <t xml:space="preserve">2026-09-01 11:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_antofagasta_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_antofagasta_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01 11:20</t>
+    <t xml:space="preserve">2026-09-04 19:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_antofagasta_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_antofagasta_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-04 19:57</t>
+    <t xml:space="preserve">2026-09-06 16:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_antofagasta_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_antofagasta_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 16:30</t>
+    <t xml:space="preserve">2026-09-08 11:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
